--- a/_data_list/Field_Force_Sample_PT.xlsx
+++ b/_data_list/Field_Force_Sample_PT.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EMIL\OneDrive\Desktop\OrangeFlow\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Telegram_Project\OrangeFlow_Dev\_data_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C6BC86-1F9C-4103-9DC4-8544655E3D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53D8AA8-BC15-4D96-9A85-0513C8CC72AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AJ$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AJ$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="169">
   <si>
     <t>DMS_CODE</t>
   </si>
@@ -495,6 +495,57 @@
   </si>
   <si>
     <t>Jubayed Miah</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>MOS0741</t>
+  </si>
+  <si>
+    <t>RS054467</t>
+  </si>
+  <si>
+    <t>Imran Hossain</t>
+  </si>
+  <si>
+    <t>R591297</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>Koilag</t>
+  </si>
+  <si>
+    <t>Rajib</t>
+  </si>
+  <si>
+    <t>Uncle</t>
+  </si>
+  <si>
+    <t>SSC</t>
+  </si>
+  <si>
+    <t>Bajitpur Hafez A. Razzak Pilot High School</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>Koilag, Bajitpur, Kishoreganj.</t>
+  </si>
+  <si>
+    <t>Abdul Hekim</t>
+  </si>
+  <si>
+    <t>Rokeya Begum</t>
+  </si>
+  <si>
+    <t>M/s Shaha Kutub Enterprise</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -554,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -564,11 +615,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -866,12 +947,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ23"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -880,12 +961,12 @@
     <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -893,10 +974,9 @@
     <col min="22" max="22" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="27" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="27.5703125" bestFit="1" customWidth="1"/>
@@ -904,7 +984,7 @@
     <col min="33" max="33" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="8" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
@@ -941,7 +1021,7 @@
       <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1048,6 +1128,9 @@
       <c r="K2" s="2">
         <v>45505</v>
       </c>
+      <c r="M2" t="s">
+        <v>157</v>
+      </c>
       <c r="N2" s="2">
         <v>37174</v>
       </c>
@@ -1095,6 +1178,9 @@
       <c r="K3" s="2">
         <v>44896</v>
       </c>
+      <c r="M3" t="s">
+        <v>157</v>
+      </c>
       <c r="N3" s="2">
         <v>36392</v>
       </c>
@@ -1142,6 +1228,9 @@
       <c r="K4" s="2">
         <v>43132</v>
       </c>
+      <c r="M4" t="s">
+        <v>157</v>
+      </c>
       <c r="N4" s="2">
         <v>34856</v>
       </c>
@@ -1189,6 +1278,9 @@
       <c r="K5" s="2">
         <v>43160</v>
       </c>
+      <c r="M5" t="s">
+        <v>157</v>
+      </c>
       <c r="N5" s="2">
         <v>29571</v>
       </c>
@@ -1236,6 +1328,9 @@
       <c r="K6" s="2">
         <v>43525</v>
       </c>
+      <c r="M6" t="s">
+        <v>157</v>
+      </c>
       <c r="N6" s="2">
         <v>37235</v>
       </c>
@@ -1283,6 +1378,9 @@
       <c r="K7" s="2">
         <v>45840</v>
       </c>
+      <c r="M7" t="s">
+        <v>157</v>
+      </c>
       <c r="N7" s="2">
         <v>38178</v>
       </c>
@@ -1330,6 +1428,12 @@
       <c r="K8" s="2">
         <v>46062</v>
       </c>
+      <c r="L8" s="2">
+        <v>46142</v>
+      </c>
+      <c r="M8" t="s">
+        <v>157</v>
+      </c>
       <c r="N8" s="2">
         <v>38716</v>
       </c>
@@ -1343,77 +1447,127 @@
         <v>2311030477929</v>
       </c>
       <c r="AJ8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E9">
-        <v>1915270106</v>
-      </c>
-      <c r="G9">
-        <v>1935591815</v>
-      </c>
-      <c r="H9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9">
-        <v>8500</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="E9" s="6">
+        <v>1915270103</v>
+      </c>
+      <c r="F9" s="6">
+        <v>1764864677</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1935591914</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I9" s="6">
+        <v>9500</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="2">
-        <v>45909</v>
-      </c>
-      <c r="N9" s="2">
-        <v>37448</v>
-      </c>
-      <c r="O9" t="s">
-        <v>70</v>
-      </c>
-      <c r="P9" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>2311030377356</v>
-      </c>
-      <c r="AJ9" t="s">
+      <c r="K9" s="7">
+        <v>46143</v>
+      </c>
+      <c r="L9" s="7"/>
+      <c r="M9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="N9" s="7">
+        <v>38512</v>
+      </c>
+      <c r="O9" s="8">
+        <v>7824872522</v>
+      </c>
+      <c r="Q9" s="9"/>
+      <c r="T9" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="V9" s="6">
+        <v>1742609199</v>
+      </c>
+      <c r="W9" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="X9" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y9" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA9" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB9" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC9" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD9" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE9" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>9000</v>
+      </c>
+      <c r="AG9" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH9" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI9" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ9" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10">
-        <v>1915300196</v>
+        <v>1915270106</v>
       </c>
       <c r="G10">
-        <v>1935591797</v>
+        <v>1935591815</v>
       </c>
       <c r="H10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I10">
         <v>8500</v>
@@ -1422,19 +1576,22 @@
         <v>59</v>
       </c>
       <c r="K10" s="2">
-        <v>45873</v>
+        <v>45909</v>
+      </c>
+      <c r="M10" t="s">
+        <v>157</v>
       </c>
       <c r="N10" s="2">
-        <v>36526</v>
+        <v>37448</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P10" t="s">
         <v>60</v>
       </c>
       <c r="Q10" s="3">
-        <v>2311580115485</v>
+        <v>2311030377356</v>
       </c>
       <c r="AJ10" t="s">
         <v>81</v>
@@ -1442,25 +1599,25 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
       <c r="E11">
-        <v>1937600512</v>
+        <v>1915300196</v>
       </c>
       <c r="G11">
-        <v>1935591796</v>
+        <v>1935591797</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11">
         <v>8500</v>
@@ -1469,19 +1626,22 @@
         <v>59</v>
       </c>
       <c r="K11" s="2">
-        <v>45976</v>
+        <v>45873</v>
+      </c>
+      <c r="M11" t="s">
+        <v>157</v>
       </c>
       <c r="N11" s="2">
-        <v>38644</v>
+        <v>36526</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
         <v>60</v>
       </c>
       <c r="Q11" s="3">
-        <v>1731580447892</v>
+        <v>2311580115485</v>
       </c>
       <c r="AJ11" t="s">
         <v>81</v>
@@ -1489,25 +1649,25 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D12" t="s">
         <v>58</v>
       </c>
       <c r="E12">
-        <v>1984217911</v>
+        <v>1937600512</v>
       </c>
       <c r="G12">
-        <v>1935591918</v>
+        <v>1935591796</v>
       </c>
       <c r="H12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I12">
         <v>8500</v>
@@ -1516,19 +1676,22 @@
         <v>59</v>
       </c>
       <c r="K12" s="2">
-        <v>45909</v>
+        <v>45976</v>
+      </c>
+      <c r="M12" t="s">
+        <v>157</v>
       </c>
       <c r="N12" s="2">
-        <v>35458</v>
+        <v>38644</v>
       </c>
       <c r="O12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P12" t="s">
         <v>60</v>
       </c>
       <c r="Q12" s="3">
-        <v>2311030047576</v>
+        <v>1731580447892</v>
       </c>
       <c r="AJ12" t="s">
         <v>81</v>
@@ -1536,25 +1699,25 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D13" t="s">
         <v>58</v>
       </c>
       <c r="E13">
-        <v>1984217912</v>
+        <v>1984217911</v>
       </c>
       <c r="G13">
-        <v>1935591999</v>
+        <v>1935591918</v>
       </c>
       <c r="H13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I13">
         <v>8500</v>
@@ -1563,19 +1726,22 @@
         <v>59</v>
       </c>
       <c r="K13" s="2">
-        <v>45965</v>
+        <v>45909</v>
+      </c>
+      <c r="M13" t="s">
+        <v>157</v>
       </c>
       <c r="N13" s="2">
-        <v>38845</v>
+        <v>35458</v>
       </c>
       <c r="O13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P13" t="s">
         <v>60</v>
       </c>
       <c r="Q13" s="3">
-        <v>2311030422596</v>
+        <v>2311030047576</v>
       </c>
       <c r="AJ13" t="s">
         <v>81</v>
@@ -1583,25 +1749,25 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
         <v>58</v>
       </c>
       <c r="E14">
-        <v>1984220363</v>
+        <v>1984217912</v>
       </c>
       <c r="G14">
-        <v>1935591917</v>
+        <v>1935591999</v>
       </c>
       <c r="H14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I14">
         <v>8500</v>
@@ -1610,19 +1776,22 @@
         <v>59</v>
       </c>
       <c r="K14" s="2">
-        <v>45748</v>
+        <v>45965</v>
+      </c>
+      <c r="M14" t="s">
+        <v>157</v>
       </c>
       <c r="N14" s="2">
-        <v>33898</v>
+        <v>38845</v>
       </c>
       <c r="O14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P14" t="s">
         <v>60</v>
       </c>
       <c r="Q14" s="3">
-        <v>1731580062730</v>
+        <v>2311030422596</v>
       </c>
       <c r="AJ14" t="s">
         <v>81</v>
@@ -1630,25 +1799,25 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D15" t="s">
         <v>58</v>
       </c>
       <c r="E15">
-        <v>1984220364</v>
+        <v>1984220363</v>
       </c>
       <c r="G15">
-        <v>1935591855</v>
+        <v>1935591917</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15">
         <v>8500</v>
@@ -1657,19 +1826,22 @@
         <v>59</v>
       </c>
       <c r="K15" s="2">
-        <v>45999</v>
+        <v>45748</v>
+      </c>
+      <c r="M15" t="s">
+        <v>157</v>
       </c>
       <c r="N15" s="2">
-        <v>37991</v>
+        <v>33898</v>
       </c>
       <c r="O15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P15" t="s">
         <v>60</v>
       </c>
       <c r="Q15" s="3">
-        <v>1737348886514</v>
+        <v>1731580062730</v>
       </c>
       <c r="AJ15" t="s">
         <v>81</v>
@@ -1677,46 +1849,49 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D16" t="s">
         <v>58</v>
       </c>
       <c r="E16">
-        <v>1984220365</v>
+        <v>1984220364</v>
       </c>
       <c r="G16">
-        <v>1935591913</v>
+        <v>1935591855</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I16">
-        <v>8404</v>
+        <v>8500</v>
       </c>
       <c r="J16" t="s">
         <v>59</v>
       </c>
       <c r="K16" s="2">
-        <v>43709</v>
+        <v>45999</v>
+      </c>
+      <c r="M16" t="s">
+        <v>157</v>
       </c>
       <c r="N16" s="2">
-        <v>36114</v>
+        <v>37991</v>
       </c>
       <c r="O16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P16" t="s">
         <v>60</v>
       </c>
       <c r="Q16" s="3">
-        <v>1731030011132</v>
+        <v>1737348886514</v>
       </c>
       <c r="AJ16" t="s">
         <v>81</v>
@@ -1724,46 +1899,49 @@
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>58</v>
       </c>
       <c r="E17">
-        <v>1984220366</v>
+        <v>1984220365</v>
       </c>
       <c r="G17">
-        <v>1935592054</v>
+        <v>1935591913</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I17">
-        <v>8580</v>
+        <v>8404</v>
       </c>
       <c r="J17" t="s">
         <v>59</v>
       </c>
       <c r="K17" s="2">
-        <v>44470</v>
+        <v>43709</v>
+      </c>
+      <c r="M17" t="s">
+        <v>157</v>
       </c>
       <c r="N17" s="2">
-        <v>36318</v>
+        <v>36114</v>
       </c>
       <c r="O17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P17" t="s">
         <v>60</v>
       </c>
       <c r="Q17" s="3">
-        <v>1731510173296</v>
+        <v>1731030011132</v>
       </c>
       <c r="AJ17" t="s">
         <v>81</v>
@@ -1771,46 +1949,49 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
         <v>58</v>
       </c>
       <c r="E18">
-        <v>1986646474</v>
+        <v>1984220366</v>
       </c>
       <c r="G18">
-        <v>1935592053</v>
+        <v>1935592054</v>
       </c>
       <c r="H18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I18">
-        <v>9350</v>
+        <v>8580</v>
       </c>
       <c r="J18" t="s">
         <v>59</v>
       </c>
       <c r="K18" s="2">
-        <v>45444</v>
+        <v>44470</v>
+      </c>
+      <c r="M18" t="s">
+        <v>157</v>
       </c>
       <c r="N18" s="2">
-        <v>32174</v>
+        <v>36318</v>
       </c>
       <c r="O18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="3">
-        <v>7017332507958</v>
+        <v>1731510173296</v>
       </c>
       <c r="AJ18" t="s">
         <v>81</v>
@@ -1818,46 +1999,49 @@
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D19" t="s">
         <v>58</v>
       </c>
       <c r="E19">
-        <v>1986686880</v>
+        <v>1986646474</v>
       </c>
       <c r="G19">
-        <v>1935591915</v>
+        <v>1935592053</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I19">
-        <v>8500</v>
+        <v>9350</v>
       </c>
       <c r="J19" t="s">
         <v>59</v>
       </c>
       <c r="K19" s="2">
-        <v>46023</v>
+        <v>45444</v>
+      </c>
+      <c r="M19" t="s">
+        <v>157</v>
       </c>
       <c r="N19" s="2">
-        <v>36557</v>
+        <v>32174</v>
       </c>
       <c r="O19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q19" s="3">
-        <v>1731030011127</v>
+        <v>7017332507958</v>
       </c>
       <c r="AJ19" t="s">
         <v>81</v>
@@ -1865,157 +2049,225 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20">
-        <v>1912317878</v>
+        <v>58</v>
+      </c>
+      <c r="E20">
+        <v>1986686880</v>
       </c>
       <c r="G20">
-        <v>1958041930</v>
+        <v>1935591915</v>
       </c>
       <c r="H20" t="s">
-        <v>135</v>
+        <v>99</v>
+      </c>
+      <c r="I20">
+        <v>8500</v>
+      </c>
+      <c r="J20" t="s">
+        <v>59</v>
       </c>
       <c r="K20" s="2">
-        <v>42370</v>
+        <v>46023</v>
+      </c>
+      <c r="M20" t="s">
+        <v>157</v>
       </c>
       <c r="N20" s="2">
-        <v>33675</v>
+        <v>36557</v>
       </c>
       <c r="O20" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="P20" t="s">
         <v>60</v>
       </c>
       <c r="Q20" s="3">
-        <v>1731510105407</v>
+        <v>1731030011127</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
         <v>128</v>
       </c>
       <c r="F21">
-        <v>1715969790</v>
+        <v>1912317878</v>
       </c>
       <c r="G21">
-        <v>1958041928</v>
+        <v>1958041930</v>
       </c>
       <c r="H21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K21" s="2">
-        <v>41122</v>
+        <v>42370</v>
+      </c>
+      <c r="M21" t="s">
+        <v>157</v>
       </c>
       <c r="N21" s="2">
-        <v>30806</v>
+        <v>33675</v>
       </c>
       <c r="O21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P21" t="s">
         <v>60</v>
       </c>
       <c r="Q21" s="3">
-        <v>1471030170630</v>
+        <v>1731510105407</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>128</v>
       </c>
       <c r="F22">
-        <v>1711228193</v>
+        <v>1715969790</v>
       </c>
       <c r="G22">
-        <v>1935597976</v>
+        <v>1958041928</v>
       </c>
       <c r="H22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K22" s="2">
-        <v>45870</v>
+        <v>41122</v>
+      </c>
+      <c r="M22" t="s">
+        <v>157</v>
       </c>
       <c r="N22" s="2">
         <v>30806</v>
       </c>
-      <c r="O22" s="4">
-        <v>2860896055</v>
+      <c r="O22" t="s">
+        <v>126</v>
       </c>
       <c r="P22" t="s">
         <v>60</v>
       </c>
       <c r="Q22" s="3">
-        <v>1731030011382</v>
+        <v>1471030170630</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
         <v>128</v>
       </c>
       <c r="F23">
-        <v>1913453027</v>
+        <v>1711228193</v>
       </c>
       <c r="G23">
-        <v>1935597774</v>
+        <v>1935597976</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K23" s="2">
-        <v>46054</v>
+        <v>45870</v>
+      </c>
+      <c r="M23" t="s">
+        <v>157</v>
       </c>
       <c r="N23" s="2">
-        <v>37337</v>
-      </c>
-      <c r="O23" t="s">
-        <v>127</v>
+        <v>30806</v>
+      </c>
+      <c r="O23" s="4">
+        <v>2860896055</v>
       </c>
       <c r="P23" t="s">
         <v>60</v>
       </c>
       <c r="Q23" s="3">
+        <v>1731030011382</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24">
+        <v>1913453027</v>
+      </c>
+      <c r="G24">
+        <v>1935597774</v>
+      </c>
+      <c r="H24" t="s">
+        <v>136</v>
+      </c>
+      <c r="K24" s="2">
+        <v>46054</v>
+      </c>
+      <c r="M24" t="s">
+        <v>157</v>
+      </c>
+      <c r="N24" s="2">
+        <v>37337</v>
+      </c>
+      <c r="O24" t="s">
+        <v>127</v>
+      </c>
+      <c r="P24" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1731050036178</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1:O1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>